--- a/data/Alt Endeksler.xlsx
+++ b/data/Alt Endeksler.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6561" uniqueCount="1431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6561" uniqueCount="1430">
   <si>
     <t>MAHALLEKAYITNO</t>
   </si>
@@ -4304,9 +4304,6 @@
   </si>
   <si>
     <t>YOĞUN KENT</t>
-  </si>
-  <si>
-    <t>ORTA YOĞUN KENT</t>
   </si>
 </sst>
 </file>
@@ -7852,7 +7849,7 @@
         <v>130</v>
       </c>
       <c r="E89" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F89">
         <v>216</v>
@@ -12066,7 +12063,7 @@
         <v>246</v>
       </c>
       <c r="E207" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F207">
         <v>1992</v>
@@ -12107,7 +12104,7 @@
         <v>247</v>
       </c>
       <c r="E208" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F208">
         <v>4033</v>
@@ -12311,7 +12308,7 @@
         <v>253</v>
       </c>
       <c r="E214" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F214">
         <v>596</v>
@@ -12734,7 +12731,7 @@
         <v>265</v>
       </c>
       <c r="E226" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F226">
         <v>3741</v>
@@ -14138,7 +14135,7 @@
         <v>307</v>
       </c>
       <c r="E268" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F268">
         <v>2928</v>
@@ -14648,7 +14645,7 @@
         <v>322</v>
       </c>
       <c r="E283" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F283">
         <v>1155</v>
@@ -14963,7 +14960,7 @@
         <v>331</v>
       </c>
       <c r="E292" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F292">
         <v>3949</v>
@@ -15635,7 +15632,7 @@
         <v>347</v>
       </c>
       <c r="E310" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F310">
         <v>1518</v>
@@ -16552,7 +16549,7 @@
         <v>367</v>
       </c>
       <c r="E335" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F335">
         <v>2091</v>
@@ -16634,7 +16631,7 @@
         <v>369</v>
       </c>
       <c r="E337" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F337">
         <v>1243</v>
@@ -16897,7 +16894,7 @@
         <v>376</v>
       </c>
       <c r="E344" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F344">
         <v>368</v>
@@ -19101,7 +19098,7 @@
         <v>97</v>
       </c>
       <c r="E405" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F405">
         <v>907</v>
@@ -19253,7 +19250,7 @@
         <v>436</v>
       </c>
       <c r="E409" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F409">
         <v>982</v>
@@ -19411,7 +19408,7 @@
         <v>439</v>
       </c>
       <c r="E413" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F413">
         <v>1717</v>
@@ -19589,7 +19586,7 @@
         <v>444</v>
       </c>
       <c r="E418" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F418">
         <v>5747</v>
@@ -19694,7 +19691,7 @@
         <v>183</v>
       </c>
       <c r="E421" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F421">
         <v>1814</v>
@@ -19735,7 +19732,7 @@
         <v>446</v>
       </c>
       <c r="E422" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F422">
         <v>2360</v>
@@ -19808,7 +19805,7 @@
         <v>448</v>
       </c>
       <c r="E424" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F424">
         <v>1087</v>
@@ -20086,7 +20083,7 @@
         <v>455</v>
       </c>
       <c r="E431" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F431">
         <v>2008</v>
@@ -20168,7 +20165,7 @@
         <v>457</v>
       </c>
       <c r="E433" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F433">
         <v>2073</v>
@@ -20326,7 +20323,7 @@
         <v>461</v>
       </c>
       <c r="E437" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F437">
         <v>9749</v>
@@ -20440,7 +20437,7 @@
         <v>464</v>
       </c>
       <c r="E440" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F440">
         <v>4636</v>
@@ -20589,7 +20586,7 @@
         <v>467</v>
       </c>
       <c r="E444" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F444">
         <v>2803</v>
@@ -20782,7 +20779,7 @@
         <v>121</v>
       </c>
       <c r="E449" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F449">
         <v>3708</v>
@@ -21001,7 +20998,7 @@
         <v>477</v>
       </c>
       <c r="E455" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F455">
         <v>6069</v>
@@ -21419,7 +21416,7 @@
         <v>488</v>
       </c>
       <c r="E466" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F466">
         <v>1394</v>
@@ -21501,7 +21498,7 @@
         <v>490</v>
       </c>
       <c r="E468" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F468">
         <v>10569</v>
@@ -21665,7 +21662,7 @@
         <v>493</v>
       </c>
       <c r="E472" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F472">
         <v>4647</v>
@@ -21864,7 +21861,7 @@
         <v>265</v>
       </c>
       <c r="E477" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F477">
         <v>6605</v>
@@ -22028,7 +22025,7 @@
         <v>500</v>
       </c>
       <c r="E481" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F481">
         <v>4670</v>
@@ -22104,7 +22101,7 @@
         <v>502</v>
       </c>
       <c r="E483" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F483">
         <v>10754</v>
@@ -22177,7 +22174,7 @@
         <v>504</v>
       </c>
       <c r="E485" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F485">
         <v>2493</v>
@@ -22320,7 +22317,7 @@
         <v>183</v>
       </c>
       <c r="E489" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F489">
         <v>12531</v>
@@ -24662,7 +24659,7 @@
         <v>559</v>
       </c>
       <c r="E550" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F550">
         <v>4682</v>
@@ -24981,7 +24978,7 @@
         <v>564</v>
       </c>
       <c r="E558" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F558">
         <v>4030</v>
@@ -25180,7 +25177,7 @@
         <v>569</v>
       </c>
       <c r="E563" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F563">
         <v>7384</v>
@@ -25373,7 +25370,7 @@
         <v>573</v>
       </c>
       <c r="E568" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F568">
         <v>490</v>
@@ -25440,7 +25437,7 @@
         <v>575</v>
       </c>
       <c r="E570" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F570">
         <v>1283</v>
@@ -26049,7 +26046,7 @@
         <v>589</v>
       </c>
       <c r="E585" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F585">
         <v>12449</v>
@@ -26248,7 +26245,7 @@
         <v>594</v>
       </c>
       <c r="E590" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F590">
         <v>5311</v>
@@ -27418,7 +27415,7 @@
         <v>97</v>
       </c>
       <c r="E620" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F620">
         <v>2762</v>
@@ -28162,7 +28159,7 @@
         <v>639</v>
       </c>
       <c r="E641" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F641">
         <v>1044</v>
@@ -28308,7 +28305,7 @@
         <v>183</v>
       </c>
       <c r="E645" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F645">
         <v>2080</v>
@@ -28416,7 +28413,7 @@
         <v>30</v>
       </c>
       <c r="E648" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F648">
         <v>1760</v>
@@ -28457,7 +28454,7 @@
         <v>645</v>
       </c>
       <c r="E649" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F649">
         <v>695</v>
@@ -28539,7 +28536,7 @@
         <v>647</v>
       </c>
       <c r="E651" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F651">
         <v>665</v>
@@ -28703,7 +28700,7 @@
         <v>651</v>
       </c>
       <c r="E655" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F655">
         <v>983</v>
@@ -28928,7 +28925,7 @@
         <v>477</v>
       </c>
       <c r="E661" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F661">
         <v>1302</v>
@@ -29305,7 +29302,7 @@
         <v>664</v>
       </c>
       <c r="E671" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F671">
         <v>628</v>
@@ -29747,7 +29744,7 @@
         <v>80</v>
       </c>
       <c r="E682" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F682">
         <v>1789</v>
@@ -30434,7 +30431,7 @@
         <v>685</v>
       </c>
       <c r="E700" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F700">
         <v>2691</v>
@@ -30475,7 +30472,7 @@
         <v>686</v>
       </c>
       <c r="E701" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F701">
         <v>5251</v>
@@ -30516,7 +30513,7 @@
         <v>687</v>
       </c>
       <c r="E702" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F702">
         <v>4760</v>
@@ -30621,7 +30618,7 @@
         <v>690</v>
       </c>
       <c r="E705" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F705">
         <v>3377</v>
@@ -30694,7 +30691,7 @@
         <v>553</v>
       </c>
       <c r="E707" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F707">
         <v>2093</v>
@@ -30735,7 +30732,7 @@
         <v>692</v>
       </c>
       <c r="E708" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F708">
         <v>2265</v>
@@ -30919,7 +30916,7 @@
         <v>696</v>
       </c>
       <c r="E713" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F713">
         <v>1968</v>
@@ -31001,7 +30998,7 @@
         <v>698</v>
       </c>
       <c r="E715" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F715">
         <v>657</v>
@@ -31042,7 +31039,7 @@
         <v>699</v>
       </c>
       <c r="E716" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F716">
         <v>789</v>
@@ -32205,7 +32202,7 @@
         <v>722</v>
       </c>
       <c r="E747" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F747">
         <v>3167</v>
@@ -32246,7 +32243,7 @@
         <v>723</v>
       </c>
       <c r="E748" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F748">
         <v>1887</v>
@@ -32512,7 +32509,7 @@
         <v>729</v>
       </c>
       <c r="E755" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F755">
         <v>2855</v>
@@ -32918,7 +32915,7 @@
         <v>739</v>
       </c>
       <c r="E766" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F766">
         <v>1666</v>
@@ -32959,7 +32956,7 @@
         <v>740</v>
       </c>
       <c r="E767" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F767">
         <v>2907</v>
@@ -33588,7 +33585,7 @@
         <v>111</v>
       </c>
       <c r="E783" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F783">
         <v>2370</v>
@@ -33775,7 +33772,7 @@
         <v>57</v>
       </c>
       <c r="E788" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F788">
         <v>1986</v>
@@ -33816,7 +33813,7 @@
         <v>58</v>
       </c>
       <c r="E789" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F789">
         <v>1903</v>
@@ -34442,7 +34439,7 @@
         <v>771</v>
       </c>
       <c r="E805" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F805">
         <v>6317</v>
@@ -34483,7 +34480,7 @@
         <v>772</v>
       </c>
       <c r="E806" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F806">
         <v>1948</v>
@@ -34705,7 +34702,7 @@
         <v>97</v>
       </c>
       <c r="E812" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F812">
         <v>3994</v>
@@ -34781,7 +34778,7 @@
         <v>514</v>
       </c>
       <c r="E814" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F814">
         <v>4009</v>
@@ -34854,7 +34851,7 @@
         <v>121</v>
       </c>
       <c r="E816" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F816">
         <v>6745</v>
@@ -35114,7 +35111,7 @@
         <v>783</v>
       </c>
       <c r="E823" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F823">
         <v>1091</v>
@@ -35222,7 +35219,7 @@
         <v>786</v>
       </c>
       <c r="E826" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F826">
         <v>1500</v>
@@ -35470,7 +35467,7 @@
         <v>793</v>
       </c>
       <c r="E833" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F833">
         <v>537</v>
@@ -35505,7 +35502,7 @@
         <v>794</v>
       </c>
       <c r="E834" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F834">
         <v>2359</v>
@@ -35540,7 +35537,7 @@
         <v>795</v>
       </c>
       <c r="E835" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F835">
         <v>1245</v>
@@ -35575,7 +35572,7 @@
         <v>796</v>
       </c>
       <c r="E836" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F836">
         <v>2839</v>
@@ -35645,7 +35642,7 @@
         <v>30</v>
       </c>
       <c r="E838" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F838">
         <v>1651</v>
@@ -35680,7 +35677,7 @@
         <v>670</v>
       </c>
       <c r="E839" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F839">
         <v>3372</v>
@@ -35852,7 +35849,7 @@
         <v>800</v>
       </c>
       <c r="E844" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F844">
         <v>1522</v>
@@ -35989,7 +35986,7 @@
         <v>803</v>
       </c>
       <c r="E848" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F848">
         <v>891</v>
@@ -36059,7 +36056,7 @@
         <v>677</v>
       </c>
       <c r="E850" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F850">
         <v>1011</v>
@@ -36094,7 +36091,7 @@
         <v>97</v>
       </c>
       <c r="E851" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F851">
         <v>3247</v>
@@ -36129,7 +36126,7 @@
         <v>805</v>
       </c>
       <c r="E852" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F852">
         <v>1635</v>
@@ -36199,7 +36196,7 @@
         <v>106</v>
       </c>
       <c r="E854" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F854">
         <v>1120</v>
@@ -36301,7 +36298,7 @@
         <v>363</v>
       </c>
       <c r="E857" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F857">
         <v>1855</v>
@@ -36508,7 +36505,7 @@
         <v>121</v>
       </c>
       <c r="E863" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F863">
         <v>3342</v>
@@ -36578,7 +36575,7 @@
         <v>813</v>
       </c>
       <c r="E865" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F865">
         <v>1494</v>
@@ -36613,7 +36610,7 @@
         <v>814</v>
       </c>
       <c r="E866" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F866">
         <v>827</v>
@@ -36648,7 +36645,7 @@
         <v>815</v>
       </c>
       <c r="E867" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F867">
         <v>1497</v>
@@ -36683,7 +36680,7 @@
         <v>816</v>
       </c>
       <c r="E868" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F868">
         <v>11080</v>
@@ -36718,7 +36715,7 @@
         <v>817</v>
       </c>
       <c r="E869" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F869">
         <v>2162</v>
@@ -36753,7 +36750,7 @@
         <v>818</v>
       </c>
       <c r="E870" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F870">
         <v>603</v>
@@ -36788,7 +36785,7 @@
         <v>819</v>
       </c>
       <c r="E871" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F871">
         <v>2519</v>
@@ -37243,7 +37240,7 @@
         <v>40</v>
       </c>
       <c r="E884" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F884">
         <v>1955</v>
@@ -37415,7 +37412,7 @@
         <v>832</v>
       </c>
       <c r="E889" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F889">
         <v>2558</v>
@@ -37485,7 +37482,7 @@
         <v>834</v>
       </c>
       <c r="E891" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F891">
         <v>11043</v>
@@ -37520,7 +37517,7 @@
         <v>835</v>
       </c>
       <c r="E892" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F892">
         <v>16172</v>
@@ -37660,7 +37657,7 @@
         <v>839</v>
       </c>
       <c r="E896" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F896">
         <v>1165</v>
@@ -37730,7 +37727,7 @@
         <v>338</v>
       </c>
       <c r="E898" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F898">
         <v>2001</v>
@@ -37765,7 +37762,7 @@
         <v>30</v>
       </c>
       <c r="E899" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F899">
         <v>3193</v>
@@ -37832,7 +37829,7 @@
         <v>842</v>
       </c>
       <c r="E901" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F901">
         <v>469</v>
@@ -37931,7 +37928,7 @@
         <v>235</v>
       </c>
       <c r="E904" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F904">
         <v>2271</v>
@@ -37966,7 +37963,7 @@
         <v>535</v>
       </c>
       <c r="E905" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F905">
         <v>1018</v>
@@ -38138,7 +38135,7 @@
         <v>111</v>
       </c>
       <c r="E910" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F910">
         <v>1981</v>
@@ -38275,7 +38272,7 @@
         <v>851</v>
       </c>
       <c r="E914" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F914">
         <v>2740</v>
@@ -38412,7 +38409,7 @@
         <v>855</v>
       </c>
       <c r="E918" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F918">
         <v>4729</v>
@@ -38447,7 +38444,7 @@
         <v>856</v>
       </c>
       <c r="E919" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F919">
         <v>1528</v>
@@ -38514,7 +38511,7 @@
         <v>858</v>
       </c>
       <c r="E921" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F921">
         <v>478</v>
@@ -38616,7 +38613,7 @@
         <v>861</v>
       </c>
       <c r="E924" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F924">
         <v>390</v>
@@ -38747,7 +38744,7 @@
         <v>865</v>
       </c>
       <c r="E928" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F928">
         <v>1198</v>
@@ -38913,7 +38910,7 @@
         <v>869</v>
       </c>
       <c r="E933" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F933">
         <v>2191</v>
@@ -39012,7 +39009,7 @@
         <v>872</v>
       </c>
       <c r="E936" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F936">
         <v>3917</v>
@@ -39079,7 +39076,7 @@
         <v>873</v>
       </c>
       <c r="E938" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F938">
         <v>1577</v>
@@ -39114,7 +39111,7 @@
         <v>40</v>
       </c>
       <c r="E939" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F939">
         <v>966</v>
@@ -39181,7 +39178,7 @@
         <v>875</v>
       </c>
       <c r="E941" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F941">
         <v>1763</v>
@@ -39216,7 +39213,7 @@
         <v>607</v>
       </c>
       <c r="E942" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F942">
         <v>5458</v>
@@ -39251,7 +39248,7 @@
         <v>499</v>
       </c>
       <c r="E943" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F943">
         <v>1967</v>
@@ -39481,7 +39478,7 @@
         <v>882</v>
       </c>
       <c r="E950" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F950">
         <v>735</v>
@@ -39583,7 +39580,7 @@
         <v>884</v>
       </c>
       <c r="E953" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F953">
         <v>2519</v>
@@ -39618,7 +39615,7 @@
         <v>80</v>
       </c>
       <c r="E954" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F954">
         <v>863</v>
@@ -39653,7 +39650,7 @@
         <v>97</v>
       </c>
       <c r="E955" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F955">
         <v>2346</v>
@@ -39755,7 +39752,7 @@
         <v>887</v>
       </c>
       <c r="E958" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F958">
         <v>371</v>
@@ -39787,7 +39784,7 @@
         <v>121</v>
       </c>
       <c r="E959" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F959">
         <v>2234</v>
@@ -39886,7 +39883,7 @@
         <v>889</v>
       </c>
       <c r="E962" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F962">
         <v>1173</v>
@@ -39985,7 +39982,7 @@
         <v>265</v>
       </c>
       <c r="E965" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F965">
         <v>1032</v>
@@ -40250,7 +40247,7 @@
         <v>899</v>
       </c>
       <c r="E973" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F973">
         <v>1005</v>
@@ -40448,7 +40445,7 @@
         <v>905</v>
       </c>
       <c r="E979" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F979">
         <v>1368</v>
@@ -40483,7 +40480,7 @@
         <v>906</v>
       </c>
       <c r="E980" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F980">
         <v>1705</v>
@@ -40617,7 +40614,7 @@
         <v>909</v>
       </c>
       <c r="E984" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F984">
         <v>727</v>
@@ -40684,7 +40681,7 @@
         <v>889</v>
       </c>
       <c r="E986" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F986">
         <v>6038</v>
@@ -40751,7 +40748,7 @@
         <v>912</v>
       </c>
       <c r="E988" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F988">
         <v>1123</v>
@@ -40885,7 +40882,7 @@
         <v>916</v>
       </c>
       <c r="E992" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F992">
         <v>506</v>
@@ -40920,7 +40917,7 @@
         <v>917</v>
       </c>
       <c r="E993" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F993">
         <v>844</v>
@@ -40955,7 +40952,7 @@
         <v>918</v>
       </c>
       <c r="E994" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F994">
         <v>1975</v>
@@ -40990,7 +40987,7 @@
         <v>796</v>
       </c>
       <c r="E995" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F995">
         <v>1275</v>
@@ -41025,7 +41022,7 @@
         <v>30</v>
       </c>
       <c r="E996" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F996">
         <v>16108</v>
@@ -41092,7 +41089,7 @@
         <v>919</v>
       </c>
       <c r="E998" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F998">
         <v>15824</v>
@@ -41162,7 +41159,7 @@
         <v>921</v>
       </c>
       <c r="E1000" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F1000">
         <v>7911</v>
@@ -41299,7 +41296,7 @@
         <v>537</v>
       </c>
       <c r="E1004" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F1004">
         <v>1256</v>
@@ -41471,7 +41468,7 @@
         <v>927</v>
       </c>
       <c r="E1009" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F1009">
         <v>2336</v>
@@ -41605,7 +41602,7 @@
         <v>514</v>
       </c>
       <c r="E1013" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F1013">
         <v>662</v>
@@ -41940,7 +41937,7 @@
         <v>939</v>
       </c>
       <c r="E1023" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F1023">
         <v>927</v>
@@ -42010,7 +42007,7 @@
         <v>941</v>
       </c>
       <c r="E1025" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F1025">
         <v>1724</v>
@@ -42045,7 +42042,7 @@
         <v>942</v>
       </c>
       <c r="E1026" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F1026">
         <v>14337</v>
@@ -42185,7 +42182,7 @@
         <v>946</v>
       </c>
       <c r="E1030" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F1030">
         <v>4859</v>
@@ -42252,7 +42249,7 @@
         <v>568</v>
       </c>
       <c r="E1032" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F1032">
         <v>7014</v>
@@ -42421,7 +42418,7 @@
         <v>952</v>
       </c>
       <c r="E1037" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F1037">
         <v>2977</v>
@@ -42456,7 +42453,7 @@
         <v>889</v>
       </c>
       <c r="E1038" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F1038">
         <v>14902</v>
@@ -42491,7 +42488,7 @@
         <v>953</v>
       </c>
       <c r="E1039" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F1039">
         <v>887</v>
@@ -42698,7 +42695,7 @@
         <v>959</v>
       </c>
       <c r="E1045" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F1045">
         <v>1826</v>
@@ -42768,7 +42765,7 @@
         <v>961</v>
       </c>
       <c r="E1047" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F1047">
         <v>2777</v>
@@ -42867,7 +42864,7 @@
         <v>962</v>
       </c>
       <c r="E1050" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F1050">
         <v>12416</v>
@@ -42902,7 +42899,7 @@
         <v>963</v>
       </c>
       <c r="E1051" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F1051">
         <v>2789</v>
@@ -42969,7 +42966,7 @@
         <v>965</v>
       </c>
       <c r="E1053" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F1053">
         <v>1039</v>
@@ -43068,7 +43065,7 @@
         <v>968</v>
       </c>
       <c r="E1056" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F1056">
         <v>2413</v>
@@ -43170,7 +43167,7 @@
         <v>971</v>
       </c>
       <c r="E1059" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F1059">
         <v>5661</v>
@@ -43205,7 +43202,7 @@
         <v>972</v>
       </c>
       <c r="E1060" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F1060">
         <v>1108</v>
@@ -43409,7 +43406,7 @@
         <v>30</v>
       </c>
       <c r="E1066" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F1066">
         <v>2119</v>
@@ -43543,7 +43540,7 @@
         <v>451</v>
       </c>
       <c r="E1070" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F1070">
         <v>1973</v>
@@ -43965,7 +43962,7 @@
         <v>992</v>
       </c>
       <c r="E1083" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F1083">
         <v>1571</v>
@@ -44361,7 +44358,7 @@
         <v>869</v>
       </c>
       <c r="E1095" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F1095">
         <v>2672</v>
@@ -45048,7 +45045,7 @@
         <v>1022</v>
       </c>
       <c r="E1116" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F1116">
         <v>7184</v>
@@ -45153,7 +45150,7 @@
         <v>1023</v>
       </c>
       <c r="E1119" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F1119">
         <v>889</v>
@@ -45290,7 +45287,7 @@
         <v>97</v>
       </c>
       <c r="E1123" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F1123">
         <v>2568</v>
@@ -45325,7 +45322,7 @@
         <v>1026</v>
       </c>
       <c r="E1124" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F1124">
         <v>2481</v>
@@ -45392,7 +45389,7 @@
         <v>1028</v>
       </c>
       <c r="E1126" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F1126">
         <v>14261</v>
@@ -45494,7 +45491,7 @@
         <v>1031</v>
       </c>
       <c r="E1129" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F1129">
         <v>1251</v>
@@ -45634,7 +45631,7 @@
         <v>121</v>
       </c>
       <c r="E1133" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F1133">
         <v>1157</v>
@@ -45975,7 +45972,7 @@
         <v>1041</v>
       </c>
       <c r="E1143" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F1143">
         <v>5094</v>
@@ -46042,7 +46039,7 @@
         <v>1043</v>
       </c>
       <c r="E1145" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F1145">
         <v>1418</v>
@@ -46348,7 +46345,7 @@
         <v>183</v>
       </c>
       <c r="E1154" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F1154">
         <v>4556</v>
@@ -46552,7 +46549,7 @@
         <v>1053</v>
       </c>
       <c r="E1160" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F1160">
         <v>827</v>
@@ -46715,7 +46712,7 @@
         <v>97</v>
       </c>
       <c r="E1165" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F1165">
         <v>3579</v>
@@ -46878,7 +46875,7 @@
         <v>1059</v>
       </c>
       <c r="E1170" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F1170">
         <v>3887</v>
@@ -46913,7 +46910,7 @@
         <v>1060</v>
       </c>
       <c r="E1171" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F1171">
         <v>3682</v>
@@ -47306,7 +47303,7 @@
         <v>1071</v>
       </c>
       <c r="E1183" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F1183">
         <v>3740</v>
@@ -47827,7 +47824,7 @@
         <v>1082</v>
       </c>
       <c r="E1199" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F1199">
         <v>827</v>
@@ -47926,7 +47923,7 @@
         <v>246</v>
       </c>
       <c r="E1202" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F1202">
         <v>3357</v>
@@ -48089,7 +48086,7 @@
         <v>1087</v>
       </c>
       <c r="E1207" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F1207">
         <v>561</v>
@@ -48386,7 +48383,7 @@
         <v>820</v>
       </c>
       <c r="E1216" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F1216">
         <v>2329</v>
@@ -48453,7 +48450,7 @@
         <v>577</v>
       </c>
       <c r="E1218" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F1218">
         <v>3789</v>
@@ -48715,7 +48712,7 @@
         <v>953</v>
       </c>
       <c r="E1226" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F1226">
         <v>3263</v>
@@ -49085,7 +49082,7 @@
         <v>1109</v>
       </c>
       <c r="E1237" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F1237">
         <v>1782</v>
@@ -49120,7 +49117,7 @@
         <v>1110</v>
       </c>
       <c r="E1238" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F1238">
         <v>2340</v>
@@ -49836,7 +49833,7 @@
         <v>671</v>
       </c>
       <c r="E1260" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F1260">
         <v>9194</v>
@@ -49871,7 +49868,7 @@
         <v>1128</v>
       </c>
       <c r="E1261" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F1261">
         <v>6760</v>
@@ -50101,7 +50098,7 @@
         <v>1134</v>
       </c>
       <c r="E1268" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F1268">
         <v>1046</v>
@@ -50171,7 +50168,7 @@
         <v>1136</v>
       </c>
       <c r="E1270" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F1270">
         <v>939</v>
@@ -50736,7 +50733,7 @@
         <v>1150</v>
       </c>
       <c r="E1287" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F1287">
         <v>940</v>
@@ -51866,7 +51863,7 @@
         <v>1181</v>
       </c>
       <c r="E1321" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F1321">
         <v>19001</v>
@@ -51936,7 +51933,7 @@
         <v>1182</v>
       </c>
       <c r="E1323" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F1323">
         <v>1252</v>
@@ -52763,7 +52760,7 @@
         <v>1201</v>
       </c>
       <c r="E1348" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F1348">
         <v>1615</v>
@@ -52999,7 +52996,7 @@
         <v>1206</v>
       </c>
       <c r="E1355" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F1355">
         <v>956</v>
@@ -54272,7 +54269,7 @@
         <v>689</v>
       </c>
       <c r="E1393" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F1393">
         <v>502</v>
@@ -55105,7 +55102,7 @@
         <v>1257</v>
       </c>
       <c r="E1418" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F1418">
         <v>602</v>
@@ -56715,7 +56712,7 @@
         <v>1297</v>
       </c>
       <c r="E1467" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F1467">
         <v>864</v>
@@ -57417,7 +57414,7 @@
         <v>733</v>
       </c>
       <c r="E1488" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F1488">
         <v>8415</v>
@@ -57551,7 +57548,7 @@
         <v>605</v>
       </c>
       <c r="E1492" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F1492">
         <v>1794</v>
@@ -57656,7 +57653,7 @@
         <v>738</v>
       </c>
       <c r="E1495" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F1495">
         <v>2337</v>
@@ -58413,7 +58410,7 @@
         <v>1335</v>
       </c>
       <c r="E1518" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F1518">
         <v>625</v>
@@ -58827,7 +58824,7 @@
         <v>1345</v>
       </c>
       <c r="E1530" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F1530">
         <v>8959</v>
@@ -61902,7 +61899,7 @@
         <v>1412</v>
       </c>
       <c r="E1620" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="F1620">
         <v>1202</v>
